--- a/workbook/implementation-tracker-workbook.xlsx
+++ b/workbook/implementation-tracker-workbook.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookups" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phases and Gates" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requests and Handoffs" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escalation Rules" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks and Issues" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness Scorecard" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity Inputs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Log" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lookups" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Projects" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Phases and Gates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tasks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Requests and Handoffs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Escalation Rules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Risks and Issues" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Readiness Scorecard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Capacity Inputs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Event Log" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="KPI Summary" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="calculation_as_of_at">'README'!$D$10</definedName>
@@ -290,13 +290,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -320,7 +320,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -360,8 +360,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -384,7 +384,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -399,9 +399,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/workbook/implementation-tracker-workbook.xlsx
+++ b/workbook/implementation-tracker-workbook.xlsx
@@ -354,6 +354,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -372,9 +373,11 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="1"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -1309,7 +1312,7 @@
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1767,25 +1770,25 @@
   <dimension ref="A1:W39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="31" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="29" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="60" customWidth="1" min="23" max="23"/>
@@ -5161,18 +5164,18 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8211,16 +8214,16 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -9193,22 +9196,22 @@
   <dimension ref="A1:W173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
     <col width="60" customWidth="1" min="12" max="12"/>
     <col width="32" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
     <col width="26" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
@@ -16407,24 +16410,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -16881,43 +16884,43 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="14" customWidth="1" min="29" max="29"/>
     <col width="14" customWidth="1" min="30" max="30"/>
     <col width="14" customWidth="1" min="31" max="31"/>
     <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="21" customWidth="1" min="33" max="33"/>
+    <col width="26" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
     <col width="40" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="17" customWidth="1" min="40" max="40"/>
+    <col width="18" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
@@ -18847,21 +18850,21 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
     <col width="26" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -21567,39 +21570,39 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
     <col width="28" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
     <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="29" max="29"/>
     <col width="20" customWidth="1" min="30" max="30"/>
     <col width="20" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="18" customWidth="1" min="35" max="35"/>
-    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="17" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="19" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
     <col width="22" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
@@ -22727,18 +22730,18 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
     <col width="70" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
   </cols>
@@ -23744,34 +23747,34 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="34" customWidth="1" min="23" max="23"/>
-    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="44" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
     <col width="34" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
     <col width="22" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
@@ -24858,31 +24861,31 @@
   <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="60" customWidth="1" min="27" max="27"/>
     <col width="22" customWidth="1" min="28" max="28"/>
   </cols>
